--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-coverage.xlsx
@@ -280,7 +280,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -318,16 +318,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -453,7 +453,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -645,22 +645,22 @@
     <t>Coverage.identifier.use</t>
   </si>
   <si>
-    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -682,22 +682,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -715,16 +715,16 @@
     <t>Coverage.identifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/clins/Idsystem/JP_Insurance_memberID</t>
@@ -751,7 +751,7 @@
 要素を省略する、とある場合には、長さ０の文字列とする。詳細は「被保険者個人識別子」の文字列仕様を参照のこと</t>
   </si>
   <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -776,7 +776,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
